--- a/Inventory/Assets/Excel/Condition/ConditionData.xlsx
+++ b/Inventory/Assets/Excel/Condition/ConditionData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\00 GitHub\Game_Team\Assets\Excel\Condition\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\00 GitHub\Game_Team\Inventory\Assets\Excel\Condition\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8EFF63D-DB0F-4A7E-B49D-E3117EB051F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F34816-FB04-4C15-90D9-486D076EABAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConditionAbility" sheetId="1" r:id="rId1"/>
@@ -516,7 +516,7 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -536,7 +536,7 @@
         <v>8</v>
       </c>
       <c r="C4">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>100</v>
@@ -556,16 +556,16 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">

--- a/Inventory/Assets/Excel/Condition/ConditionData.xlsx
+++ b/Inventory/Assets/Excel/Condition/ConditionData.xlsx
@@ -1,36 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\00 GitHub\Game_Team\Inventory\Assets\Excel\Condition\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Create\00_SourceTree\Game_Team\Inventory\Assets\Excel\Condition\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F34816-FB04-4C15-90D9-486D076EABAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F6C953B-73A8-4BFC-A554-E55A62C7E7E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConditionAbility" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -525,7 +513,7 @@
         <v>10</v>
       </c>
       <c r="F3">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
